--- a/data/trans_camb/P05B_R-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P05B_R-Provincia-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,12; 2,71</t>
+          <t>-2,7; 2,54</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 6,73</t>
+          <t>-0,35; 6,45</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,14; -0,54</t>
+          <t>-4,87; -0,44</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,11; 4,81</t>
+          <t>-0,29; 4,93</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,98; 6,97</t>
+          <t>1,04; 6,8</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-3,25; -0,39</t>
+          <t>-3,22; -0,39</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 2,71</t>
+          <t>-0,89; 3,16</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,18; 5,75</t>
+          <t>1,18; 5,71</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-3,24; -0,67</t>
+          <t>-3,34; -0,72</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-90,47%</t>
+          <t>-90,46%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-93,53%</t>
+          <t>-93,72%</t>
         </is>
       </c>
     </row>
@@ -783,12 +783,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-78,29; 374,59</t>
+          <t>-74,74; 283,82</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-25,93; 640,49</t>
+          <t>-22,05; 602,47</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-27,96; —</t>
+          <t>-44,08; 946,75</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>16,98; 1440,54</t>
+          <t>1,96; 1502,31</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -813,17 +813,17 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-43,02; 294,51</t>
+          <t>-36,18; 417,68</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>19,84; 601,34</t>
+          <t>28,92; 677,72</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; -43,07</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-2,83</t>
+          <t>-2,85</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-4,81</t>
+          <t>-4,85</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-3,83</t>
+          <t>-3,86</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 4,11</t>
+          <t>-1,31; 4,18</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,47; 1,25</t>
+          <t>-3,46; 1,02</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,95; -0,98</t>
+          <t>-5,18; -1,2</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,26; 1,31</t>
+          <t>-4,17; 1,17</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-3,56; 2,05</t>
+          <t>-3,25; 2,16</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-7,41; -2,9</t>
+          <t>-7,09; -2,95</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-2,22; 1,53</t>
+          <t>-1,92; 1,78</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-2,76; 1,09</t>
+          <t>-2,64; 1,0</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-5,49; -2,5</t>
+          <t>-5,35; -2,48</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-77,73%</t>
+          <t>-78,23%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-86,38%</t>
+          <t>-87,06%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-83,0%</t>
+          <t>-83,62%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-29,58; 174,12</t>
+          <t>-29,5; 163,63</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-68,18; 65,59</t>
+          <t>-69,99; 45,89</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -20,99</t>
+          <t>-94,71; -29,38</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-61,2; 37,68</t>
+          <t>-60,44; 31,74</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-51,62; 49,26</t>
+          <t>-48,74; 54,82</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-95,4; -65,85</t>
+          <t>-95,55; -70,63</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-38,75; 40,7</t>
+          <t>-35,74; 52,8</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-48,69; 33,34</t>
+          <t>-47,89; 28,9</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-92,39; -63,23</t>
+          <t>-93,25; -66,36</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0,3</t>
+          <t>0,12</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-3,27</t>
+          <t>-3,4</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-1,54</t>
+          <t>-1,7</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-6,14; -2,06</t>
+          <t>-6,25; -2,12</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,46; -1,02</t>
+          <t>-5,67; -0,9</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,64; 3,66</t>
+          <t>-2,68; 3,65</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-9,15; -3,81</t>
+          <t>-9,33; -3,77</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-8,88; -3,45</t>
+          <t>-8,74; -3,46</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-6,35; -0,24</t>
+          <t>-6,56; -0,36</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-6,97; -3,3</t>
+          <t>-6,81; -3,41</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-6,42; -2,84</t>
+          <t>-6,53; -2,83</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-3,78; 0,8</t>
+          <t>-3,9; 0,46</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-50,93%</t>
+          <t>-52,93%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-30,34%</t>
+          <t>-33,44%</t>
         </is>
       </c>
     </row>
@@ -1220,42 +1220,42 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 8,91</t>
+          <t>-100,0; 33,74</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-56,18; 160,27</t>
+          <t>-56,05; 152,77</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -71,45</t>
+          <t>-100,0; -74,24</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -63,07</t>
+          <t>-100,0; -53,64</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-74,69; 0,38</t>
+          <t>-76,93; 3,97</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -80,59</t>
+          <t>-100,0; -84,09</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-97,85; -62,23</t>
+          <t>-97,61; -66,13</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-59,98; 23,89</t>
+          <t>-61,1; 13,21</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0,13</t>
+          <t>-0,28</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-0,74</t>
+          <t>-0,39</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-0,39</t>
+          <t>-0,34</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,6; 0,68</t>
+          <t>-3,28; 0,75</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,8; 0,29</t>
+          <t>-3,68; 0,41</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,43; 3,06</t>
+          <t>-2,52; 2,36</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,74; 1,52</t>
+          <t>-2,84; 1,57</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,86; 3,08</t>
+          <t>-2,25; 3,01</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-3,02; 1,03</t>
+          <t>-2,47; 1,42</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-2,52; 0,53</t>
+          <t>-2,58; 0,46</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,35; 1,12</t>
+          <t>-2,23; 1,09</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-2,17; 1,27</t>
+          <t>-1,94; 1,38</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>-10,19%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-26,8%</t>
+          <t>-14,27%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-14,27%</t>
+          <t>-12,36%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-87,82; 61,6</t>
+          <t>-84,71; 62,38</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-88,18; 35,82</t>
+          <t>-88,19; 39,12</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-62,09; 195,57</t>
+          <t>-62,93; 162,74</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-70,99; 100,67</t>
+          <t>-73,04; 102,26</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-51,34; 179,23</t>
+          <t>-56,62; 202,27</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-70,92; 61,93</t>
+          <t>-62,07; 92,2</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-68,21; 30,91</t>
+          <t>-70,61; 29,34</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-63,06; 59,35</t>
+          <t>-62,14; 66,61</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-55,27; 62,03</t>
+          <t>-52,08; 80,28</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-7,12</t>
+          <t>-7,13</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-9,6</t>
+          <t>-9,58</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-8,39</t>
+          <t>-8,37</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-9,41; -0,99</t>
+          <t>-9,42; -1,21</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-11,77; -4,34</t>
+          <t>-11,94; -4,55</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-11,22; -3,78</t>
+          <t>-11,28; -3,92</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-11,78; -2,5</t>
+          <t>-13,05; -2,83</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-13,01; -4,26</t>
+          <t>-13,84; -4,3</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-14,58; -6,07</t>
+          <t>-14,17; -5,97</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-9,16; -2,97</t>
+          <t>-9,21; -2,75</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-10,86; -5,23</t>
+          <t>-11,08; -5,23</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-11,36; -5,77</t>
+          <t>-11,61; -6,07</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-95,16%</t>
+          <t>-95,35%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-98,75%</t>
+          <t>-98,47%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-97,44%</t>
+          <t>-97,18%</t>
         </is>
       </c>
     </row>
@@ -1647,7 +1647,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-90,76; -7,38</t>
+          <t>-89,63; -7,6</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1657,37 +1657,37 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -69,98</t>
+          <t>-100,0; -62,72</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-89,17; -24,0</t>
+          <t>-91,6; -30,7</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-96,39; -54,72</t>
+          <t>-97,02; -54,16</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -90,62</t>
+          <t>-100,0; -90,03</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-85,69; -39,06</t>
+          <t>-84,01; -35,42</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-98,08; -75,07</t>
+          <t>-97,85; -74,67</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -87,82</t>
+          <t>-100,0; -86,09</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>-0,26</t>
+          <t>-0,33</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,14 +1729,14 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
+          <t>-0,96</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
           <t>-0,92</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>-0,92</t>
-        </is>
-      </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
           <t>-1,14</t>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-0,6</t>
+          <t>-0,65</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-1,87; 1,16</t>
+          <t>-2,09; 1,12</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-2,62; 0,31</t>
+          <t>-2,59; 0,31</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-1,94; 1,48</t>
+          <t>-1,89; 1,33</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-3,57; 0,02</t>
+          <t>-3,68; 0,05</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-3,8; -0,03</t>
+          <t>-3,73; -0,03</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-3,05; 0,68</t>
+          <t>-3,47; 0,64</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-2,27; 0,17</t>
+          <t>-2,25; 0,18</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-2,43; -0,19</t>
+          <t>-2,46; -0,15</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-1,96; 0,57</t>
+          <t>-1,88; 0,51</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>-23,96%</t>
+          <t>-30,26%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-49,06%</t>
+          <t>-51,25%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-40,25%</t>
+          <t>-43,88%</t>
         </is>
       </c>
     </row>
@@ -1888,22 +1888,22 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-90,71; 141,88</t>
+          <t>-93,11; 134,31</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 64,24</t>
+          <t>-100,0; 56,43</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 29,19</t>
+          <t>-100,0; 26,47</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-84,93; 88,96</t>
+          <t>-81,63; 108,81</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>-1,45</t>
+          <t>-1,41</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-4,9</t>
+          <t>-4,53</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>-3,15</t>
+          <t>-2,99</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-2,85; -0,24</t>
+          <t>-2,71; -0,26</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-2,26; 0,59</t>
+          <t>-2,21; 0,61</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-2,83; -0,26</t>
+          <t>-2,81; -0,23</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-7,94; -3,59</t>
+          <t>-7,92; -3,62</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-7,11; -2,72</t>
+          <t>-7,02; -2,76</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-7,29; -2,72</t>
+          <t>-6,72; -2,68</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-4,81; -2,17</t>
+          <t>-4,96; -2,51</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-4,27; -1,53</t>
+          <t>-4,26; -1,57</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-4,54; -1,96</t>
+          <t>-4,38; -1,79</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>-68,47%</t>
+          <t>-66,73%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-75,76%</t>
+          <t>-70,1%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>-72,64%</t>
+          <t>-69,09%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-90,24; -0,2</t>
+          <t>-90,01; -5,15</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-75,89; 57,12</t>
+          <t>-80,49; 56,17</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-92,13; 9,07</t>
+          <t>-90,45; -3,3</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-96,11; -61,6</t>
+          <t>-96,18; -60,78</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-86,64; -47,64</t>
+          <t>-87,44; -52,19</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-90,2; -53,46</t>
+          <t>-83,26; -51,51</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-91,65; -60,94</t>
+          <t>-92,05; -65,6</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-80,3; -40,66</t>
+          <t>-80,69; -41,41</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-85,35; -53,8</t>
+          <t>-82,01; -48,66</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>-2,19</t>
+          <t>-2,09</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>-2,97</t>
+          <t>-3,01</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>-2,62</t>
+          <t>-2,56</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-3,17; -0,21</t>
+          <t>-3,19; -0,25</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-3,89; -1,26</t>
+          <t>-3,92; -1,3</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-3,75; -0,96</t>
+          <t>-3,55; -0,89</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-4,56; -1,65</t>
+          <t>-4,46; -1,64</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-4,42; -1,44</t>
+          <t>-4,39; -1,52</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-4,66; -1,67</t>
+          <t>-4,57; -1,69</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-3,44; -1,28</t>
+          <t>-3,4; -1,26</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-3,78; -1,72</t>
+          <t>-3,62; -1,71</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-3,65; -1,71</t>
+          <t>-3,55; -1,62</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>-84,56%</t>
+          <t>-80,54%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>-81,15%</t>
+          <t>-82,24%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>-83,24%</t>
+          <t>-81,57%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-87,83; 4,36</t>
+          <t>-87,46; -1,63</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -65,07</t>
+          <t>-100,0; -65,04</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-97,01; -48,91</t>
+          <t>-95,11; -39,7</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-94,11; -52,53</t>
+          <t>-94,16; -57,36</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-92,27; -47,33</t>
+          <t>-91,92; -49,15</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-93,11; -56,86</t>
+          <t>-93,29; -59,99</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-85,94; -46,68</t>
+          <t>-86,59; -46,78</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-92,76; -62,85</t>
+          <t>-92,77; -65,4</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-93,08; -65,95</t>
+          <t>-90,7; -65,03</t>
         </is>
       </c>
     </row>
@@ -2377,7 +2377,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>-3,46</t>
+          <t>-3,41</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>-2,68</t>
+          <t>-2,65</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-2,03; -0,53</t>
+          <t>-2,04; -0,57</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-2,3; -0,8</t>
+          <t>-2,32; -0,91</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-2,55; -1,13</t>
+          <t>-2,57; -1,2</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-3,95; -2,26</t>
+          <t>-3,92; -2,24</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-3,48; -1,68</t>
+          <t>-3,54; -1,77</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-4,33; -2,68</t>
+          <t>-4,22; -2,62</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-2,71; -1,59</t>
+          <t>-2,76; -1,64</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-2,68; -1,53</t>
+          <t>-2,71; -1,53</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-3,2; -2,12</t>
+          <t>-3,17; -2,13</t>
         </is>
       </c>
     </row>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>-63,46%</t>
+          <t>-63,51%</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>-73,84%</t>
+          <t>-72,75%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>-69,87%</t>
+          <t>-69,22%</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-60,6; -20,57</t>
+          <t>-60,55; -22,58</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-68,37; -31,68</t>
+          <t>-68,54; -33,87</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-75,45; -43,0</t>
+          <t>-75,21; -45,68</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-75,45; -53,51</t>
+          <t>-74,84; -51,95</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-65,78; -39,58</t>
+          <t>-66,53; -40,91</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-81,54; -64,06</t>
+          <t>-80,34; -63,61</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-65,27; -46,11</t>
+          <t>-65,84; -46,23</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-63,75; -43,66</t>
+          <t>-64,08; -43,4</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-76,91; -61,6</t>
+          <t>-76,13; -61,83</t>
         </is>
       </c>
     </row>
